--- a/doc/Acompanhamento de Projetos.xlsx
+++ b/doc/Acompanhamento de Projetos.xlsx
@@ -16,13 +16,41 @@
     <author/>
   </authors>
   <commentList>
+    <comment authorId="0" ref="A128">
+      <text>
+        <t xml:space="preserve">Podemos usar as bibliotecas:
+- OpenAI Whisper
+- SpeechRecognition combinada com a PyAudio</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="A109">
       <text>
         <t xml:space="preserve">Podemos usar as bibliotecas:
 - Twilio</t>
       </text>
     </comment>
+    <comment authorId="0" ref="A156">
+      <text>
+        <t xml:space="preserve">Podemos usar as bibliotecas:
+- OpenAI Whisper
+- SpeechRecognition combinada com a PyAudio</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="A138">
+      <text>
+        <t xml:space="preserve">Podemos usar as bibliotecas:
+- OpenAI Whisper
+- SpeechRecognition combinada com a PyAudio</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="A119">
+      <text>
+        <t xml:space="preserve">Podemos usar as bibliotecas:
+- OpenAI Whisper
+- SpeechRecognition combinada com a PyAudio</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="A147">
       <text>
         <t xml:space="preserve">Podemos usar as bibliotecas:
 - OpenAI Whisper
@@ -34,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
   <si>
     <t xml:space="preserve">TÍTULO DO PROJETO: Agrobook
 ÁREA DE APLICAÇÃO:  Agronomia
@@ -383,13 +411,133 @@
     <t>RF011 - Inserção de dados por voz</t>
   </si>
   <si>
-    <t>dd/mm/yyyy</t>
-  </si>
-  <si>
-    <t>A fazer</t>
+    <t>16/06/2026</t>
   </si>
   <si>
     <t>3 VA</t>
+  </si>
+  <si>
+    <t>1 - Agricultor clica no botão de microfone</t>
+  </si>
+  <si>
+    <t>2 - Sistema inicia gravação de 5 segundos via sounddevice (16000 Hz)</t>
+  </si>
+  <si>
+    <t>3 - Sistema salva áudio em arquivo .wav temporário</t>
+  </si>
+  <si>
+    <t>4 - Sistema envia para Whisper (Groq) com language="pt"</t>
+  </si>
+  <si>
+    <t>5 - Sistema retorna texto transcrito e deleta o arquivo temporário</t>
+  </si>
+  <si>
+    <t>- Silêncio ou áudio vazio - retorna erro "Não ouvi nada. Tente falar mais perto do microfone."</t>
+  </si>
+  <si>
+    <t>- Erro na API Whisper - retorna string vazia e exibe erro no terminal</t>
+  </si>
+  <si>
+    <t>RF012 - Interpretação da fala do agricultor via LLM</t>
+  </si>
+  <si>
+    <t>1 - Sistema recebe texto transcrito pelo Whisper</t>
+  </si>
+  <si>
+    <t>2 - Sistema monta prompt com instruções e envia para llama-3.3-70b via Groq</t>
+  </si>
+  <si>
+    <t>3 - LLM classifica o tipo da fala (plantio, colheita, gasto, nome, cpf, cidade, etc.)</t>
+  </si>
+  <si>
+    <t>4 - LLM extrai os campos correspondentes ao tipo identificado</t>
+  </si>
+  <si>
+    <t>5 - Sistema retorna dicionário estruturado para preencher a tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - JSON malformado - fallback com raw_decode tenta recuperar os dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - API offline ou erro - retorna tipo "desconhecido" com texto original</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Fala não identificada - tipo "desconhecido", campos ficam em branco</t>
+  </si>
+  <si>
+    <t>RF013- Desambiguação por contexto de tela</t>
+  </si>
+  <si>
+    <t>1 - Tela identifica seu próprio contexto (plantio, colheita, gasto, coproprietario)</t>
+  </si>
+  <si>
+    <t>2 - Sistema anexa o contexto à fala antes de enviar ao LLM (ex: "[Contexto: colheita] dez sacos de milho")</t>
+  </si>
+  <si>
+    <t>3 - LLM usa o contexto para classificar corretamente mesmo sem verbo explícito</t>
+  </si>
+  <si>
+    <t>4 - Sistema retorna dados classificados conforme a tela atual</t>
+  </si>
+  <si>
+    <t>5 - Campos da tela são preenchidos com os dados extraídos</t>
+  </si>
+  <si>
+    <t>- Sem contexto - LLM tenta inferir pelo verbo da fala</t>
+  </si>
+  <si>
+    <t>- Ambiguidade sem contexto - retorna tipo "desconhecido"</t>
+  </si>
+  <si>
+    <t>RF014 - Botão de microfone reutilizável</t>
+  </si>
+  <si>
+    <t>1 - Tela solicita criação do botão via make_mic_button()</t>
+  </si>
+  <si>
+    <t>2 - Tela conecta o botão ao campo alvo via attach_voice_to_lineedit()</t>
+  </si>
+  <si>
+    <t>3 - Agricultor clica - botão muda para vermelho e desabilita</t>
+  </si>
+  <si>
+    <t>4 - Sistema executa gravação e chamadas à API em thread separada</t>
+  </si>
+  <si>
+    <t>5 - Ao finalizar, botão volta ao verde e exibe o texto transcrito no status</t>
+  </si>
+  <si>
+    <t>- Erro na thread - botão reabilitado, exibe mensagem de erro no status</t>
+  </si>
+  <si>
+    <t>- Ícone não encontrado - botão renderizado sem ícone como fallback</t>
+  </si>
+  <si>
+    <t>RF015 - Normalização de medidas e datas via LLM</t>
+  </si>
+  <si>
+    <t>1 - Sistema recebe campo individual digitado ou falado (ex: "uns três saco", "ontonte")</t>
+  </si>
+  <si>
+    <t>2 - Sistema identifica se o campo é data ou quantidade</t>
+  </si>
+  <si>
+    <t>3 - Envia para LLM com prompt específico (DATE_PROMPT ou AMOUNT_PROMPT)</t>
+  </si>
+  <si>
+    <t>4 - LLM converte para formato canônico (dd/mm/yyyy ou kg/ha/litro)</t>
+  </si>
+  <si>
+    <t>5 - Sistema exibe valor original e valor convertido, ambos salvos no registro</t>
+  </si>
+  <si>
+    <t>- Expressão não reconhecida - mantém texto original sem conversão</t>
+  </si>
+  <si>
+    <t>- Data inválida no calendário - exibe erro e pede novamente</t>
+  </si>
+  <si>
+    <t>- Já está no formato correto (dd/mm/yyyy) - não chama o LLM, retorna direto</t>
   </si>
 </sst>
 </file>
@@ -615,7 +763,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -715,8 +863,6 @@
     <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2094,37 +2240,43 @@
         <v>115</v>
       </c>
       <c r="D119" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="18" t="s">
         <v>116</v>
-      </c>
-      <c r="E119" s="18" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="19"/>
-      <c r="B120" s="35"/>
+      <c r="B120" s="33" t="s">
+        <v>117</v>
+      </c>
       <c r="C120" s="19"/>
       <c r="D120" s="19"/>
       <c r="E120" s="19"/>
     </row>
     <row r="121">
       <c r="A121" s="19"/>
-      <c r="B121" s="35"/>
+      <c r="B121" s="33" t="s">
+        <v>118</v>
+      </c>
       <c r="C121" s="19"/>
       <c r="D121" s="19"/>
       <c r="E121" s="19"/>
     </row>
     <row r="122">
       <c r="A122" s="19"/>
-      <c r="B122" s="35"/>
+      <c r="B122" s="33" t="s">
+        <v>119</v>
+      </c>
       <c r="C122" s="19"/>
       <c r="D122" s="19"/>
       <c r="E122" s="19"/>
     </row>
     <row r="123">
       <c r="A123" s="19"/>
-      <c r="B123" s="32" t="s">
-        <v>28</v>
+      <c r="B123" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="C123" s="19"/>
       <c r="D123" s="19"/>
@@ -2132,30 +2284,419 @@
     </row>
     <row r="124">
       <c r="A124" s="19"/>
-      <c r="B124" s="35"/>
+      <c r="B124" s="33" t="s">
+        <v>121</v>
+      </c>
       <c r="C124" s="19"/>
       <c r="D124" s="19"/>
       <c r="E124" s="19"/>
     </row>
     <row r="125">
       <c r="A125" s="19"/>
-      <c r="B125" s="35"/>
+      <c r="B125" s="32" t="s">
+        <v>28</v>
+      </c>
       <c r="C125" s="19"/>
       <c r="D125" s="19"/>
       <c r="E125" s="19"/>
     </row>
     <row r="126">
-      <c r="A126" s="23"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="23"/>
-      <c r="D126" s="23"/>
-      <c r="E126" s="23"/>
+      <c r="A126" s="19"/>
+      <c r="B126" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="C126" s="19"/>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="23"/>
+      <c r="B127" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19"/>
+      <c r="B129" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129" s="19"/>
+      <c r="D129" s="19"/>
+      <c r="E129" s="19"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="19"/>
+      <c r="B130" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C130" s="19"/>
+      <c r="D130" s="19"/>
+      <c r="E130" s="19"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="19"/>
+      <c r="B131" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C131" s="19"/>
+      <c r="D131" s="19"/>
+      <c r="E131" s="19"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="19"/>
+      <c r="B132" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C132" s="19"/>
+      <c r="D132" s="19"/>
+      <c r="E132" s="19"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="19"/>
+      <c r="B133" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C133" s="19"/>
+      <c r="D133" s="19"/>
+      <c r="E133" s="19"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="19"/>
+      <c r="B134" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134" s="19"/>
+      <c r="D134" s="19"/>
+      <c r="E134" s="19"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="19"/>
+      <c r="B135" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C135" s="19"/>
+      <c r="D135" s="19"/>
+      <c r="E135" s="19"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="19"/>
+      <c r="B136" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C136" s="19"/>
+      <c r="D136" s="19"/>
+      <c r="E136" s="19"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="23"/>
+      <c r="B137" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B138" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19"/>
+      <c r="B139" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C139" s="19"/>
+      <c r="D139" s="19"/>
+      <c r="E139" s="19"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="19"/>
+      <c r="B140" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C140" s="19"/>
+      <c r="D140" s="19"/>
+      <c r="E140" s="19"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="19"/>
+      <c r="B141" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C141" s="19"/>
+      <c r="D141" s="19"/>
+      <c r="E141" s="19"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="19"/>
+      <c r="B142" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C142" s="19"/>
+      <c r="D142" s="19"/>
+      <c r="E142" s="19"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="19"/>
+      <c r="B143" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C143" s="19"/>
+      <c r="D143" s="19"/>
+      <c r="E143" s="19"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="19"/>
+      <c r="B144" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C144" s="19"/>
+      <c r="D144" s="19"/>
+      <c r="E144" s="19"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="19"/>
+      <c r="B145" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145" s="19"/>
+      <c r="D145" s="19"/>
+      <c r="E145" s="19"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="23"/>
+      <c r="B146" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C146" s="23"/>
+      <c r="D146" s="23"/>
+      <c r="E146" s="23"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B147" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="19"/>
+      <c r="B148" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C148" s="19"/>
+      <c r="D148" s="19"/>
+      <c r="E148" s="19"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="19"/>
+      <c r="B149" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C149" s="19"/>
+      <c r="D149" s="19"/>
+      <c r="E149" s="19"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="19"/>
+      <c r="B150" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150" s="19"/>
+      <c r="D150" s="19"/>
+      <c r="E150" s="19"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="19"/>
+      <c r="B151" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C151" s="19"/>
+      <c r="D151" s="19"/>
+      <c r="E151" s="19"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="19"/>
+      <c r="B152" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19"/>
+      <c r="E152" s="19"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="19"/>
+      <c r="B153" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C153" s="19"/>
+      <c r="D153" s="19"/>
+      <c r="E153" s="19"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="19"/>
+      <c r="B154" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19"/>
+      <c r="E154" s="19"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="23"/>
+      <c r="B155" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C155" s="23"/>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B156" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D156" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E156" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="19"/>
+      <c r="B157" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" s="19"/>
+      <c r="D157" s="19"/>
+      <c r="E157" s="19"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="19"/>
+      <c r="B158" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C158" s="19"/>
+      <c r="D158" s="19"/>
+      <c r="E158" s="19"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="19"/>
+      <c r="B159" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C159" s="19"/>
+      <c r="D159" s="19"/>
+      <c r="E159" s="19"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="19"/>
+      <c r="B160" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C160" s="19"/>
+      <c r="D160" s="19"/>
+      <c r="E160" s="19"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="19"/>
+      <c r="B161" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C161" s="19"/>
+      <c r="D161" s="19"/>
+      <c r="E161" s="19"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="19"/>
+      <c r="B162" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C162" s="19"/>
+      <c r="D162" s="19"/>
+      <c r="E162" s="19"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="19"/>
+      <c r="B163" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C163" s="19"/>
+      <c r="D163" s="19"/>
+      <c r="E163" s="19"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="19"/>
+      <c r="B164" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C164" s="19"/>
+      <c r="D164" s="19"/>
+      <c r="E164" s="19"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="23"/>
+      <c r="B165" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C165" s="23"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="61">
     <mergeCell ref="D98:D108"/>
     <mergeCell ref="D109:D118"/>
-    <mergeCell ref="D119:D126"/>
+    <mergeCell ref="D119:D127"/>
     <mergeCell ref="D71:D79"/>
     <mergeCell ref="E71:E79"/>
     <mergeCell ref="D80:D88"/>
@@ -2163,16 +2704,19 @@
     <mergeCell ref="D89:D97"/>
     <mergeCell ref="E89:E97"/>
     <mergeCell ref="E98:E108"/>
+    <mergeCell ref="A128:A137"/>
+    <mergeCell ref="A138:A146"/>
+    <mergeCell ref="A147:A155"/>
+    <mergeCell ref="A156:A165"/>
+    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="A71:A79"/>
+    <mergeCell ref="A80:A88"/>
+    <mergeCell ref="A89:A97"/>
+    <mergeCell ref="A98:A108"/>
+    <mergeCell ref="A109:A118"/>
+    <mergeCell ref="A119:A127"/>
     <mergeCell ref="D27:D37"/>
     <mergeCell ref="E27:E37"/>
-    <mergeCell ref="C27:C37"/>
-    <mergeCell ref="C38:C49"/>
-    <mergeCell ref="C71:C79"/>
-    <mergeCell ref="C80:C88"/>
-    <mergeCell ref="C89:C97"/>
-    <mergeCell ref="C98:C108"/>
-    <mergeCell ref="C109:C118"/>
-    <mergeCell ref="C119:C126"/>
     <mergeCell ref="D38:D49"/>
     <mergeCell ref="E38:E49"/>
     <mergeCell ref="A1:B1"/>
@@ -2182,13 +2726,6 @@
     <mergeCell ref="E5:E26"/>
     <mergeCell ref="A27:A37"/>
     <mergeCell ref="A38:A49"/>
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="A71:A79"/>
-    <mergeCell ref="A80:A88"/>
-    <mergeCell ref="A89:A97"/>
-    <mergeCell ref="A98:A108"/>
-    <mergeCell ref="A109:A118"/>
-    <mergeCell ref="A119:A126"/>
     <mergeCell ref="A50:A62"/>
     <mergeCell ref="C50:C62"/>
     <mergeCell ref="D50:D62"/>
@@ -2197,13 +2734,33 @@
     <mergeCell ref="D63:D70"/>
     <mergeCell ref="E63:E70"/>
     <mergeCell ref="E109:E118"/>
-    <mergeCell ref="E119:E126"/>
+    <mergeCell ref="E119:E127"/>
+    <mergeCell ref="E128:E137"/>
+    <mergeCell ref="E138:E146"/>
+    <mergeCell ref="E147:E155"/>
+    <mergeCell ref="C27:C37"/>
+    <mergeCell ref="C38:C49"/>
+    <mergeCell ref="C71:C79"/>
+    <mergeCell ref="C80:C88"/>
+    <mergeCell ref="C89:C97"/>
+    <mergeCell ref="C98:C108"/>
+    <mergeCell ref="C109:C118"/>
+    <mergeCell ref="C156:C165"/>
+    <mergeCell ref="D156:D165"/>
+    <mergeCell ref="E156:E165"/>
+    <mergeCell ref="C119:C127"/>
+    <mergeCell ref="C128:C137"/>
+    <mergeCell ref="D128:D137"/>
+    <mergeCell ref="C138:C146"/>
+    <mergeCell ref="D138:D146"/>
+    <mergeCell ref="C147:C155"/>
+    <mergeCell ref="D147:D155"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D5 D27 D38 D50 D63 D71 D80 D89 D98 D109 D119">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D5 D27 D38 D50 D63 D71 D80 D89 D98 D109 D119 D128 D138 D147 D156">
       <formula1>"Pronta,Em desenvolvimento,A fazer"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E5 E27 E38 E50 E63 E71 E80 E89 E98 E109 E119">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E5 E27 E38 E50 E63 E71 E80 E89 E98 E109 E119 E128 E138 E147 E156">
       <formula1>"P1 - Altíssima,P2 - Alta,P3 - Regular,P4 - Baixa,P5 - Baixíssima,NA - Não aplicável,1 VA,2 VA,3 VA"</formula1>
     </dataValidation>
   </dataValidations>
